--- a/Filtered/HCA_Florida_Highlands_Hospital.xlsx
+++ b/Filtered/HCA_Florida_Highlands_Hospital.xlsx
@@ -579,6 +579,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -636,6 +641,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -713,6 +723,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -770,6 +785,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -847,6 +867,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -904,6 +929,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -981,6 +1011,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1038,6 +1073,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1115,6 +1155,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1172,6 +1217,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1249,6 +1299,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1326,6 +1381,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1383,6 +1443,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1460,6 +1525,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1517,6 +1587,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1594,6 +1669,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1651,6 +1731,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1728,6 +1813,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1785,6 +1875,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1847,6 +1942,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1904,6 +2004,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1981,6 +2086,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2038,6 +2148,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2115,6 +2230,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2172,6 +2292,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2249,6 +2374,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2306,6 +2436,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2383,6 +2518,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2440,6 +2580,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2517,6 +2662,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2574,6 +2724,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2651,6 +2806,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2728,6 +2888,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2785,6 +2950,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2862,6 +3032,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2919,6 +3094,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2996,6 +3176,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3053,6 +3238,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3115,6 +3305,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3172,6 +3367,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3249,6 +3449,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3306,6 +3511,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3383,6 +3593,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3440,6 +3655,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3517,6 +3737,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3574,6 +3799,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3651,6 +3881,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3708,6 +3943,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3785,6 +4025,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3842,6 +4087,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3919,6 +4169,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3996,6 +4251,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4053,6 +4313,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4130,6 +4395,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4187,6 +4457,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4264,6 +4539,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4321,6 +4601,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4398,6 +4683,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4455,6 +4745,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4517,6 +4812,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4574,6 +4874,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4651,6 +4956,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4708,6 +5018,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4785,6 +5100,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4842,6 +5162,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4919,6 +5244,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4976,6 +5306,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5053,6 +5388,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5110,6 +5450,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5172,6 +5517,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5229,6 +5579,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5306,6 +5661,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5363,6 +5723,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5440,6 +5805,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5497,6 +5867,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5574,6 +5949,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5631,6 +6011,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5708,6 +6093,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5765,6 +6155,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5842,6 +6237,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5899,6 +6299,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5976,6 +6381,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6033,6 +6443,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6110,6 +6525,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6167,6 +6587,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6244,6 +6669,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6301,6 +6731,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6378,6 +6813,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6435,6 +6875,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6512,6 +6957,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6569,6 +7019,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6646,6 +7101,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6703,6 +7163,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6780,6 +7245,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6837,6 +7307,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6914,6 +7389,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6971,6 +7451,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7048,6 +7533,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7105,6 +7595,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7182,6 +7677,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7239,6 +7739,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7316,6 +7821,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7373,6 +7883,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7450,6 +7965,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7507,6 +8027,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7584,6 +8109,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7641,6 +8171,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7718,6 +8253,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7775,6 +8315,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7852,6 +8397,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7929,6 +8479,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7986,6 +8541,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8063,6 +8623,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8140,6 +8705,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8197,6 +8767,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8274,6 +8849,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8331,6 +8911,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8408,6 +8993,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8485,6 +9075,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8542,6 +9137,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8619,6 +9219,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8676,6 +9281,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8753,6 +9363,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8830,6 +9445,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8887,6 +9507,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8964,6 +9589,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9021,6 +9651,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9098,6 +9733,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9155,6 +9795,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9232,6 +9877,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9289,6 +9939,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9351,6 +10006,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9408,6 +10068,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9470,6 +10135,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9532,6 +10202,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9589,6 +10264,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9666,6 +10346,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9723,6 +10408,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9800,6 +10490,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9857,6 +10552,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9934,6 +10634,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9991,6 +10696,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10068,6 +10778,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10125,6 +10840,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10202,6 +10922,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10259,6 +10984,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10336,6 +11066,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10393,6 +11128,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10470,6 +11210,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10527,6 +11272,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10604,6 +11354,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10661,6 +11416,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10738,6 +11498,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10795,6 +11560,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10872,6 +11642,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10929,6 +11704,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11006,6 +11786,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11063,6 +11848,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11140,6 +11930,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11197,6 +11992,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11274,6 +12074,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11331,6 +12136,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11408,6 +12218,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11485,6 +12300,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11542,6 +12362,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11604,6 +12429,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11661,6 +12491,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11723,6 +12558,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11780,6 +12620,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11857,6 +12702,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11914,6 +12764,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11991,6 +12846,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12048,6 +12908,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12125,6 +12990,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12182,6 +13052,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12259,6 +13134,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12316,6 +13196,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12393,6 +13278,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12450,6 +13340,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12527,6 +13422,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12584,6 +13484,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12661,6 +13566,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12718,6 +13628,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12795,6 +13710,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12852,6 +13772,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12929,6 +13854,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12986,6 +13916,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13063,6 +13998,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13120,6 +14060,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13197,6 +14142,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13254,6 +14204,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13331,6 +14286,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13388,6 +14348,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13465,6 +14430,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13522,6 +14492,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13599,6 +14574,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13656,6 +14636,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13733,6 +14718,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13790,6 +14780,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13867,6 +14862,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13924,6 +14924,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14001,6 +15006,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14058,6 +15068,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14135,6 +15150,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14192,6 +15212,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14269,6 +15294,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14326,6 +15356,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14403,6 +15438,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14460,6 +15500,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14537,6 +15582,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14594,6 +15644,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14671,6 +15726,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14728,6 +15788,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14805,6 +15870,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14862,6 +15932,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14939,6 +16014,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14996,6 +16076,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15073,6 +16158,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15130,6 +16220,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15207,6 +16302,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15264,6 +16364,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15341,6 +16446,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15398,6 +16508,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15475,6 +16590,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15532,6 +16652,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15594,6 +16719,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15651,6 +16781,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15728,6 +16863,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15785,6 +16925,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15862,6 +17007,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15919,6 +17069,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15996,6 +17151,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16073,6 +17233,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16130,6 +17295,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16207,6 +17377,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16264,6 +17439,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16341,6 +17521,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16398,6 +17583,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16475,6 +17665,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16532,6 +17727,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16609,6 +17809,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16666,6 +17871,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16743,6 +17953,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16820,6 +18035,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16877,6 +18097,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16954,6 +18179,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17011,6 +18241,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17088,6 +18323,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17165,6 +18405,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17222,6 +18467,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17299,6 +18549,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17356,6 +18611,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17433,6 +18693,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17490,6 +18755,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17567,6 +18837,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17624,6 +18899,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17701,6 +18981,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17758,6 +19043,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17835,6 +19125,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17892,6 +19187,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17969,6 +19269,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18026,6 +19331,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18103,6 +19413,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18160,6 +19475,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18237,6 +19557,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18294,6 +19619,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18371,6 +19701,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18428,6 +19763,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18505,6 +19845,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18562,6 +19907,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18639,6 +19989,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18696,6 +20051,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18773,6 +20133,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18830,6 +20195,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18907,6 +20277,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18964,6 +20339,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19041,6 +20421,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19118,6 +20503,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19175,6 +20565,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19252,6 +20647,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19309,6 +20709,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19386,6 +20791,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19463,6 +20873,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19520,6 +20935,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19597,6 +21017,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19654,6 +21079,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19731,6 +21161,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19788,6 +21223,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19865,6 +21305,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19922,6 +21367,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19999,6 +21449,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20056,6 +21511,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20118,6 +21578,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20175,6 +21640,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20252,6 +21722,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20309,6 +21784,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20386,6 +21866,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20443,6 +21928,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20520,6 +22010,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20577,6 +22072,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20639,6 +22139,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20701,6 +22206,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20758,6 +22268,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20835,6 +22350,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20892,6 +22412,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20969,6 +22494,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21026,6 +22556,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21088,6 +22623,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21145,6 +22685,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21222,6 +22767,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21279,6 +22829,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21356,6 +22911,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21413,6 +22973,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21490,6 +23055,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21547,6 +23117,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21624,6 +23199,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21681,6 +23261,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21743,6 +23328,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21800,6 +23390,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21877,6 +23472,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21934,6 +23534,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22011,6 +23616,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22068,6 +23678,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22145,6 +23760,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22202,6 +23822,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22279,6 +23904,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22336,6 +23966,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22413,6 +24048,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22470,6 +24110,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22547,6 +24192,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22604,6 +24254,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22666,6 +24321,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22723,6 +24383,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22800,6 +24465,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22857,6 +24527,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22934,6 +24609,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22991,6 +24671,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23068,6 +24753,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23125,6 +24815,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23202,6 +24897,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23259,6 +24959,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23336,6 +25041,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23393,6 +25103,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23470,6 +25185,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23527,6 +25247,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23604,6 +25329,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23661,6 +25391,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23738,6 +25473,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23795,6 +25535,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23872,6 +25617,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23929,6 +25679,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24006,6 +25761,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24063,6 +25823,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24140,6 +25905,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24197,6 +25967,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24274,6 +26049,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24331,6 +26111,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24408,6 +26193,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24465,6 +26255,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24542,6 +26337,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24599,6 +26399,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24661,6 +26466,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24723,6 +26533,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24785,6 +26600,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24842,6 +26662,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24919,6 +26744,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24976,6 +26806,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25038,6 +26873,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25100,6 +26940,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25162,6 +27007,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25224,6 +27074,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25286,6 +27141,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25343,6 +27203,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25420,6 +27285,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25477,6 +27347,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25554,6 +27429,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25611,6 +27491,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25673,6 +27558,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25735,6 +27625,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25792,6 +27687,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25869,6 +27769,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25926,6 +27831,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26003,6 +27913,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26060,6 +27975,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26122,6 +28042,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26184,6 +28109,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26246,6 +28176,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26303,6 +28238,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26380,6 +28320,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26437,6 +28382,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26514,6 +28464,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26571,6 +28526,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26633,6 +28593,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26690,6 +28655,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26752,6 +28722,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26809,6 +28784,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26871,6 +28851,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26933,6 +28918,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26995,6 +28985,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27052,6 +29047,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27129,6 +29129,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27186,6 +29191,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27248,6 +29258,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27305,6 +29320,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27367,6 +29387,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27429,6 +29454,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27491,6 +29521,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27548,6 +29583,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27625,6 +29665,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27682,6 +29727,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27744,6 +29794,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27801,6 +29856,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27878,6 +29938,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27935,6 +30000,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27997,6 +30067,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28059,6 +30134,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28121,6 +30201,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28178,6 +30263,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28255,6 +30345,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28312,6 +30407,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28389,6 +30489,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28446,6 +30551,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28508,6 +30618,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28570,6 +30685,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28627,6 +30747,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28689,6 +30814,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28751,6 +30881,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28813,6 +30948,11 @@
           <t>COCHRA</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28868,6 +31008,11 @@
       <c r="K430" t="inlineStr">
         <is>
           <t>COCHRA</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
